--- a/Demo/MDA/demo_mda_9999_5_supervision_hf.xlsx
+++ b/Demo/MDA/demo_mda_9999_5_supervision_hf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885C6C77-AE6D-4DB7-9981-666BCBFB4B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB0F2E1-DC43-4F88-9F0E-4F850FFBF00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="331">
   <si>
     <t>type</t>
   </si>
@@ -114,12 +114,6 @@
     <t>Recommandations superviseur</t>
   </si>
   <si>
-    <t>geopoint</t>
-  </si>
-  <si>
-    <t>Coordonnées GPS</t>
-  </si>
-  <si>
     <t>list_name</t>
   </si>
   <si>
@@ -405,9 +399,6 @@
     <t>s_recommandations</t>
   </si>
   <si>
-    <t>s_gps</t>
-  </si>
-  <si>
     <t>state</t>
   </si>
   <si>
@@ -592,12 +583,6 @@
   </si>
   <si>
     <t>${s_nb_villages_non_treated} &gt; 0</t>
-  </si>
-  <si>
-    <t>${s_state}</t>
-  </si>
-  <si>
-    <t>${s_district}</t>
   </si>
   <si>
     <t>disease</t>
@@ -900,9 +885,6 @@
     <t>Village</t>
   </si>
   <si>
-    <t>${s_health_facility}</t>
-  </si>
-  <si>
     <t>Misangi</t>
   </si>
   <si>
@@ -1030,13 +1012,25 @@
   </si>
   <si>
     <t>s_follow_side_effect_procedure</t>
+  </si>
+  <si>
+    <t>attitude_health_worker</t>
+  </si>
+  <si>
+    <t>state = ${s_state}</t>
+  </si>
+  <si>
+    <t>district = ${s_district}</t>
+  </si>
+  <si>
+    <t>health_facility = ${s_health_facility}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1080,8 +1074,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1097,12 +1099,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1135,7 +1131,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1195,7 +1191,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1513,7 +1511,7 @@
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="29.85546875" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1526,60 +1524,60 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="10"/>
@@ -1598,13 +1596,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5"/>
@@ -1623,15 +1621,15 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
@@ -1643,8 +1641,8 @@
         <v>7</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>190</v>
+      <c r="L4" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1652,15 +1650,15 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
@@ -1672,8 +1670,8 @@
         <v>7</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>191</v>
+      <c r="L5" s="16" t="s">
+        <v>329</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1681,15 +1679,15 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
@@ -1701,8 +1699,8 @@
         <v>7</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>289</v>
+      <c r="L6" s="22" t="s">
+        <v>330</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1715,10 +1713,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5"/>
@@ -1742,10 +1740,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
@@ -1766,13 +1764,13 @@
     </row>
     <row r="9" spans="1:21" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="16"/>
@@ -1797,21 +1795,21 @@
     </row>
     <row r="10" spans="1:21" s="17" customFormat="1" ht="374.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="16"/>
       <c r="F10" s="22" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -1835,10 +1833,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5" t="s">
@@ -1862,10 +1860,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5"/>
@@ -1889,10 +1887,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5"/>
@@ -1916,10 +1914,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5"/>
@@ -1943,17 +1941,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="6"/>
       <c r="H15" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
@@ -1989,13 +1987,17 @@
       <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
+      <c r="A17" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>327</v>
+      </c>
       <c r="C17" s="24" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>11</v>
@@ -2015,13 +2017,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5"/>
@@ -2042,13 +2044,13 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
@@ -2069,13 +2071,13 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5"/>
@@ -2096,13 +2098,13 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5"/>
@@ -2123,13 +2125,13 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
@@ -2150,13 +2152,13 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5"/>
@@ -2177,13 +2179,13 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
@@ -2204,13 +2206,13 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
@@ -2231,13 +2233,13 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
@@ -2258,13 +2260,13 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
@@ -2309,10 +2311,10 @@
         <v>10</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24" t="s">
@@ -2321,7 +2323,7 @@
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I29" s="24"/>
       <c r="J29" s="24"/>
@@ -2335,13 +2337,13 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5"/>
@@ -2362,13 +2364,13 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
@@ -2389,13 +2391,13 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5"/>
@@ -2440,10 +2442,10 @@
         <v>10</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="24" t="s">
@@ -2452,7 +2454,7 @@
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
       <c r="H34" s="24" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I34" s="24"/>
       <c r="J34" s="24"/>
@@ -2466,13 +2468,13 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5"/>
@@ -2493,13 +2495,13 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
@@ -2520,13 +2522,13 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="5"/>
@@ -2571,10 +2573,10 @@
         <v>10</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -2583,7 +2585,7 @@
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="24"/>
@@ -2597,13 +2599,13 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="5"/>
@@ -2624,13 +2626,13 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5"/>
@@ -2651,13 +2653,13 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
@@ -2702,10 +2704,10 @@
         <v>10</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="24" t="s">
@@ -2714,7 +2716,7 @@
       <c r="F44" s="24"/>
       <c r="G44" s="24"/>
       <c r="H44" s="24" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="24"/>
@@ -2728,13 +2730,13 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5"/>
@@ -2755,13 +2757,13 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5"/>
@@ -2782,13 +2784,13 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="5"/>
@@ -2833,10 +2835,10 @@
         <v>10</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="24" t="s">
@@ -2845,7 +2847,7 @@
       <c r="F49" s="24"/>
       <c r="G49" s="24"/>
       <c r="H49" s="24" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="24"/>
@@ -2859,13 +2861,13 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5"/>
@@ -2886,13 +2888,13 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5"/>
@@ -2913,13 +2915,13 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="5"/>
@@ -2964,10 +2966,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D54" s="24"/>
       <c r="E54" s="24" t="s">
@@ -2976,7 +2978,7 @@
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
       <c r="H54" s="24" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I54" s="24"/>
       <c r="J54" s="24"/>
@@ -2990,13 +2992,13 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5"/>
@@ -3017,13 +3019,13 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5"/>
@@ -3044,13 +3046,13 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="5"/>
@@ -3095,10 +3097,10 @@
         <v>10</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="24" t="s">
@@ -3107,7 +3109,7 @@
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
       <c r="H59" s="24" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I59" s="24"/>
       <c r="J59" s="24"/>
@@ -3121,13 +3123,13 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="5"/>
@@ -3148,13 +3150,13 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="5"/>
@@ -3175,13 +3177,13 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="5"/>
@@ -3226,10 +3228,10 @@
         <v>10</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="24" t="s">
@@ -3238,7 +3240,7 @@
       <c r="F64" s="24"/>
       <c r="G64" s="24"/>
       <c r="H64" s="24" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
@@ -3252,13 +3254,13 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="5"/>
@@ -3279,13 +3281,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="5"/>
@@ -3306,13 +3308,13 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="5"/>
@@ -3376,10 +3378,10 @@
         <v>10</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="5" t="s">
@@ -3403,10 +3405,10 @@
         <v>12</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="5"/>
@@ -3430,10 +3432,10 @@
         <v>12</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="5"/>
@@ -3454,13 +3456,13 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="5"/>
@@ -3505,7 +3507,7 @@
         <v>10</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>16</v>
@@ -3529,10 +3531,10 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>17</v>
@@ -3559,7 +3561,7 @@
         <v>18</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>19</v>
@@ -3607,7 +3609,7 @@
         <v>10</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>20</v>
@@ -3634,7 +3636,7 @@
         <v>12</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>21</v>
@@ -3661,7 +3663,7 @@
         <v>12</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>22</v>
@@ -3709,7 +3711,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>23</v>
@@ -3733,10 +3735,10 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -3760,10 +3762,10 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>25</v>
@@ -3811,7 +3813,7 @@
         <v>26</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>27</v>
@@ -3838,7 +3840,7 @@
         <v>26</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -3865,7 +3867,7 @@
         <v>26</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>29</v>
@@ -3888,24 +3890,16 @@
       <c r="Q89" s="5"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>31</v>
-      </c>
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="6"/>
       <c r="D90" s="6"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="6"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
-      <c r="J90" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="J90" s="5"/>
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
@@ -3973,32 +3967,41 @@
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
@@ -4007,13 +4010,13 @@
     </row>
     <row r="3" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="C3" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -4022,13 +4025,13 @@
     </row>
     <row r="4" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -4037,13 +4040,13 @@
     </row>
     <row r="5" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -4052,13 +4055,13 @@
     </row>
     <row r="6" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
@@ -4067,13 +4070,13 @@
     </row>
     <row r="7" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -4082,13 +4085,13 @@
     </row>
     <row r="8" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
@@ -4097,13 +4100,13 @@
     </row>
     <row r="9" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -4112,13 +4115,13 @@
     </row>
     <row r="10" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -4127,13 +4130,13 @@
     </row>
     <row r="11" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -4142,13 +4145,13 @@
     </row>
     <row r="12" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
@@ -4157,13 +4160,13 @@
     </row>
     <row r="13" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
@@ -4172,7 +4175,7 @@
     </row>
     <row r="14" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="14">
         <v>99</v>
@@ -4196,13 +4199,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -4211,13 +4214,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -4235,13 +4238,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -4250,13 +4253,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -4265,13 +4268,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4280,13 +4283,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -4295,13 +4298,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -4319,13 +4322,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -4334,13 +4337,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4349,13 +4352,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -4364,13 +4367,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -4379,13 +4382,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -4403,13 +4406,13 @@
     </row>
     <row r="31" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
@@ -4418,13 +4421,13 @@
     </row>
     <row r="32" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
@@ -4433,13 +4436,13 @@
     </row>
     <row r="33" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
@@ -4448,13 +4451,13 @@
     </row>
     <row r="34" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
@@ -4463,13 +4466,13 @@
     </row>
     <row r="35" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>197</v>
-      </c>
       <c r="C35" s="20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
@@ -4487,13 +4490,13 @@
     </row>
     <row r="37" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
@@ -4502,13 +4505,13 @@
     </row>
     <row r="38" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
@@ -4517,13 +4520,13 @@
     </row>
     <row r="39" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
@@ -4532,13 +4535,13 @@
     </row>
     <row r="40" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
@@ -4547,13 +4550,13 @@
     </row>
     <row r="41" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>203</v>
-      </c>
       <c r="C41" s="20" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
@@ -4562,13 +4565,13 @@
     </row>
     <row r="42" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
@@ -4577,13 +4580,13 @@
     </row>
     <row r="43" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
@@ -4592,13 +4595,13 @@
     </row>
     <row r="44" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
@@ -4607,13 +4610,13 @@
     </row>
     <row r="45" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
@@ -4622,13 +4625,13 @@
     </row>
     <row r="46" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
@@ -4646,13 +4649,13 @@
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -4661,13 +4664,13 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -4676,13 +4679,13 @@
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="C50" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -4691,13 +4694,13 @@
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -4706,13 +4709,13 @@
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -4721,13 +4724,13 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -4736,13 +4739,13 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -4751,13 +4754,13 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -4766,13 +4769,13 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -4781,13 +4784,13 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -4808,13 +4811,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
@@ -4825,13 +4828,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
@@ -4842,13 +4845,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
@@ -4859,13 +4862,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
@@ -4876,13 +4879,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
@@ -4893,13 +4896,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
@@ -4910,13 +4913,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
@@ -4927,13 +4930,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
@@ -4944,13 +4947,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
@@ -4961,13 +4964,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
@@ -4978,13 +4981,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
@@ -4995,13 +4998,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
@@ -5012,13 +5015,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
@@ -5029,13 +5032,13 @@
         <v>8</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
@@ -5046,13 +5049,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
@@ -5063,13 +5066,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
@@ -5080,13 +5083,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -5097,13 +5100,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
@@ -5114,13 +5117,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
@@ -5131,13 +5134,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
@@ -5154,681 +5157,684 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="C82" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C100" s="25"/>
+    </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C101" s="25" t="s">
-        <v>290</v>
+        <v>284</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C102" s="25" t="s">
-        <v>291</v>
+        <v>285</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>285</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>292</v>
+        <v>286</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>286</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C104" s="25" t="s">
-        <v>293</v>
+        <v>287</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>287</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C105" s="25" t="s">
-        <v>294</v>
+        <v>288</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G105" s="5"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>295</v>
+        <v>289</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C107" s="25" t="s">
-        <v>296</v>
+        <v>290</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>290</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>297</v>
+        <v>291</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>291</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C109" s="25" t="s">
-        <v>298</v>
+        <v>292</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C110" s="25" t="s">
-        <v>299</v>
+        <v>293</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>293</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>300</v>
+        <v>294</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>301</v>
+        <v>295</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>295</v>
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G112" s="5"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="C113" s="25" t="s">
-        <v>302</v>
+        <v>296</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>303</v>
+        <v>297</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>297</v>
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C115" s="25" t="s">
-        <v>304</v>
+        <v>298</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C116" s="25" t="s">
-        <v>305</v>
+        <v>299</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>299</v>
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G116" s="5"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C117" s="25" t="s">
-        <v>306</v>
+        <v>300</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>300</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G117" s="5"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>307</v>
+        <v>301</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>301</v>
       </c>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C119" s="25" t="s">
-        <v>308</v>
+        <v>302</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>302</v>
       </c>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G119" s="5"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C120" s="25" t="s">
-        <v>309</v>
+        <v>303</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>303</v>
       </c>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G120" s="5"/>
     </row>
@@ -5850,25 +5856,25 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
         <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Demo/MDA/demo_mda_9999_5_supervision_hf.xlsx
+++ b/Demo/MDA/demo_mda_9999_5_supervision_hf.xlsx
@@ -1,28 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB0F2E1-DC43-4F88-9F0E-4F850FFBF00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25BC8D4-7FB7-4952-B9A5-102E23ED30F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">survey!$A$1:$Q$57</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={018D13DF-1012-4DF6-A96B-1024C4E8D7EC}</author>
+    <author>tc={45C6829E-2510-407D-9D1B-3CE01D387F3B}</author>
+  </authors>
+  <commentList>
+    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{018D13DF-1012-4DF6-A96B-1024C4E8D7EC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Change to AZM.SUP</t>
+      </text>
+    </comment>
+    <comment ref="H48" authorId="1" shapeId="0" xr:uid="{45C6829E-2510-407D-9D1B-3CE01D387F3B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Change to AZM.TAB</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="322">
   <si>
     <t>type</t>
   </si>
@@ -66,63 +96,18 @@
     <t>no</t>
   </si>
   <si>
-    <t>select_multiple raisons_non_traitement</t>
-  </si>
-  <si>
     <t>end_group</t>
   </si>
   <si>
-    <t>Mobilisation sociale</t>
-  </si>
-  <si>
-    <t>Population informée avant campagne ?</t>
-  </si>
-  <si>
-    <t>select_multiple canaux_com</t>
-  </si>
-  <si>
-    <t>Canaux communication utilisés</t>
-  </si>
-  <si>
-    <t>Supervision terrain</t>
-  </si>
-  <si>
-    <t>Nombre DC supervisés</t>
-  </si>
-  <si>
-    <t>Nombre villages supervisés</t>
-  </si>
-  <si>
     <t>Pharmacovigilance</t>
   </si>
   <si>
-    <t>Effets indésirables signalés ?</t>
-  </si>
-  <si>
-    <t>Effets indésirables graves signalés ?</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
-    <t>Difficultés rencontrées</t>
-  </si>
-  <si>
-    <t>Solutions proposées</t>
-  </si>
-  <si>
-    <t>Recommandations superviseur</t>
-  </si>
-  <si>
     <t>list_name</t>
   </si>
   <si>
-    <t>raisons_non_traitement</t>
-  </si>
-  <si>
-    <t>canaux_com</t>
-  </si>
-  <si>
     <t>Radio</t>
   </si>
   <si>
@@ -135,12 +120,6 @@
     <t>default_language</t>
   </si>
   <si>
-    <t>(Demo) 5. MDA Supervision Health facility</t>
-  </si>
-  <si>
-    <t>demo_mda_9999_5_supervision_hf</t>
-  </si>
-  <si>
     <t>English</t>
   </si>
   <si>
@@ -348,9 +327,6 @@
     <t>s_nb_villages_non_treated</t>
   </si>
   <si>
-    <t>s_reason_non_traitement</t>
-  </si>
-  <si>
     <t>s_training</t>
   </si>
   <si>
@@ -618,18 +594,6 @@
     <t>ALB</t>
   </si>
   <si>
-    <t>TETRA.TAB</t>
-  </si>
-  <si>
-    <t>TETRA TAB</t>
-  </si>
-  <si>
-    <t>TETRA.SUSP</t>
-  </si>
-  <si>
-    <t>TETRA SUSP</t>
-  </si>
-  <si>
     <t>MEB</t>
   </si>
   <si>
@@ -651,30 +615,6 @@
     <t>You cannot select a single medicine together with its combination version</t>
   </si>
   <si>
-    <t>logistique_ivm</t>
-  </si>
-  <si>
-    <t>logistique_alb</t>
-  </si>
-  <si>
-    <t>logistique_meb</t>
-  </si>
-  <si>
-    <t>logistique_dec</t>
-  </si>
-  <si>
-    <t>logistique_pzq</t>
-  </si>
-  <si>
-    <t>logistique_az_sus</t>
-  </si>
-  <si>
-    <t>logistique_az_tab</t>
-  </si>
-  <si>
-    <t>logistique_tetra</t>
-  </si>
-  <si>
     <t>s_stock_remain_ivm</t>
   </si>
   <si>
@@ -753,18 +693,6 @@
     <t>s_disease</t>
   </si>
   <si>
-    <t>not(selected(${s_medicine}, 'IVM') and not(selected(${s_disease}, 'ONCHO'))) and
-not(selected(${s_medicine}, 'IVM+ALB') and not(selected(${s_disease}, 'LF') or selected(${s_disease}, 'ONCHO'))) and
-not(selected(${s_medicine}, 'IVM+ALB+DEC') and not(selected(${s_disease}, 'LF'))) and
-not(selected(${s_medicine}, 'ALB') and not(selected(${s_disease}, 'STH'))) and
-not(selected(${s_medicine}, 'MEB') and not(selected(${s_disease}, 'STH'))) and
-not(selected(${s_medicine}, 'PZQ') and not(selected(${s_disease}, 'SCHISTO'))) and
-not(selected(${s_medicine}, 'PZQ+ALB') and not(selected(${s_disease}, 'SCHISTO') or selected(${s_disease}, 'STH'))) and
-not(selected(${s_medicine}, 'PZQ+MEB') and not(selected(${s_disease}, 'SCHISTO') or selected(${s_disease}, 'STH'))) and
-not(selected(${s_medicine}, 'TETRA.TAB') and not(selected(${s_disease}, 'TRACHOMA'))) and
-not(selected(${s_medicine}, 'TETRA.SUSP') and not(selected(${s_disease}, 'TRACHOMA')))</t>
-  </si>
-  <si>
     <t>selected(${s_medicine}, 'IVM') or selected(${s_medicine}, 'IVM+ALB') or selected(${s_medicine}, 'IVM+ALB+DEC')</t>
   </si>
   <si>
@@ -783,12 +711,6 @@
     <t xml:space="preserve">selected(${s_medicine}, 'TETRA') </t>
   </si>
   <si>
-    <t xml:space="preserve">selected(${s_medicine}, 'TETRA.TAB') </t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${s_medicine}, 'TETRA.SUSP') </t>
-  </si>
-  <si>
     <t>Is there any Ivermectine remaining stock?</t>
   </si>
   <si>
@@ -948,75 +870,6 @@
     <t>Select the medicine package</t>
   </si>
   <si>
-    <t>Observe the actions, attitudes, and skills of the community health worker during the treatment of a family</t>
-  </si>
-  <si>
-    <t>wearing a vest, wearing a mask, using hand sanitizer, standard greetings - introduction -, administering medication, data collection</t>
-  </si>
-  <si>
-    <t>s_wear_vest</t>
-  </si>
-  <si>
-    <t>Is the community health worker/healthcare worker team identifiable by a vest?</t>
-  </si>
-  <si>
-    <t>s_usual_greetings</t>
-  </si>
-  <si>
-    <t>The DC proceeds with the usual greetings</t>
-  </si>
-  <si>
-    <t>s_introduced_patient</t>
-  </si>
-  <si>
-    <t>s_used_height_chart_correctly</t>
-  </si>
-  <si>
-    <t>s_gave_write_dosage</t>
-  </si>
-  <si>
-    <t>The DC  introduces the patient by specifying the reason for their visit and the treatment being administered.</t>
-  </si>
-  <si>
-    <t>The DC  uses the height chart correctly.</t>
-  </si>
-  <si>
-    <t>The DC  administers the medication correctly according to the height chart reading.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The medicine is taken in the presence of the DC </t>
-  </si>
-  <si>
-    <t>s_medicine_took_in_front_of_dc</t>
-  </si>
-  <si>
-    <t>Does the DC complete the data collection forms (checklist and register) correctly?</t>
-  </si>
-  <si>
-    <t>Does the DC investigate and report cases of FL, Buruli ulcer, leishmaniasis and rumours of VG?</t>
-  </si>
-  <si>
-    <t>Are ineligible individuals identified?</t>
-  </si>
-  <si>
-    <t>s_filled_form</t>
-  </si>
-  <si>
-    <t>s_investigated_cases</t>
-  </si>
-  <si>
-    <t>s_identified_ineligible</t>
-  </si>
-  <si>
-    <t>Is the procedure to follow in the event of side events known?</t>
-  </si>
-  <si>
-    <t>s_follow_side_effect_procedure</t>
-  </si>
-  <si>
-    <t>attitude_health_worker</t>
-  </si>
-  <si>
     <t>state = ${s_state}</t>
   </si>
   <si>
@@ -1024,13 +877,199 @@
   </si>
   <si>
     <t>health_facility = ${s_health_facility}</t>
+  </si>
+  <si>
+    <t>disease_filter</t>
+  </si>
+  <si>
+    <t>selected(${s_disease}, disease_filter)</t>
+  </si>
+  <si>
+    <t>not(
+  selected(${s_disease}, 'LF') and
+  selected(${s_disease}, 'ONCHO') and
+  selected(${s_medicine}, 'IVM')
+)
+and
+not(
+  selected(${s_disease}, 'STH') and
+  selected(${s_disease}, 'SCHISTO') and
+  (
+    selected(${s_medicine}, 'ALB') or
+    selected(${s_medicine}, 'MEB') or
+    selected(${s_medicine}, 'PZQ')
+  )
+)
+and
+not(
+  selected(${s_disease}, 'SCHISTO') and
+  not(selected(${s_disease}, 'STH')) and
+  (
+    selected(${s_medicine}, 'PZQ+ALB') or
+    selected(${s_medicine}, 'PZQ+MEB')
+  )
+)
+and
+not(selected(${s_medicine}, 'IVM') and not(selected(${s_disease}, 'ONCHO') and not(selected(${s_disease}, 'LF'))))
+and
+not(selected(${s_medicine}, 'IVM+ALB') and not(selected(${s_disease}, 'LF') or selected(${s_disease}, 'ONCHO')))
+and
+not(selected(${s_medicine}, 'IVM+ALB+DEC') and not(selected(${s_disease}, 'LF')))
+and
+not(selected(${s_medicine}, 'ALB') and not(selected(${s_disease}, 'STH')))
+and
+not(selected(${s_medicine}, 'MEB') and not(selected(${s_disease}, 'STH')))
+and
+not(selected(${s_medicine}, 'PZQ') and not(selected(${s_disease}, 'SCHISTO')))
+and
+not(selected(${s_medicine}, 'PZQ+ALB') and not(selected(${s_disease}, 'SCHISTO') or selected(${s_disease}, 'STH')))
+and
+not(selected(${s_medicine}, 'PZQ+MEB') and not(selected(${s_disease}, 'SCHISTO') or selected(${s_disease}, 'STH')))
+and
+not(selected(${s_medicine}, 'AZM.TAB') and not(selected(${s_disease}, 'TRACHOMA')))
+and
+not(selected(${s_medicine}, 'AZM.SUSP') and not(selected(${s_disease}, 'TRACHOMA')))
+and
+not(selected(${s_medicine}, 'TETRA') and not(selected(${s_disease}, 'TRACHOMA')))</t>
+  </si>
+  <si>
+    <t>logistic_ivm</t>
+  </si>
+  <si>
+    <t>logistic_alb</t>
+  </si>
+  <si>
+    <t>logistic_meb</t>
+  </si>
+  <si>
+    <t>logistic_dec</t>
+  </si>
+  <si>
+    <t>logistic_az_sus</t>
+  </si>
+  <si>
+    <t>logistic_az_tab</t>
+  </si>
+  <si>
+    <t>logistic_tetra</t>
+  </si>
+  <si>
+    <t>Not.Required</t>
+  </si>
+  <si>
+    <t>Not Required</t>
+  </si>
+  <si>
+    <t>select_multiple reasons_non_treatment</t>
+  </si>
+  <si>
+    <t>reasons_non_treatment</t>
+  </si>
+  <si>
+    <t>s_reason_non_treatment</t>
+  </si>
+  <si>
+    <t>logistic_pzq</t>
+  </si>
+  <si>
+    <t>AZM.TAB</t>
+  </si>
+  <si>
+    <t>AZM TAB</t>
+  </si>
+  <si>
+    <t>AZM.SUSP</t>
+  </si>
+  <si>
+    <t>AZM SUSP</t>
+  </si>
+  <si>
+    <t>TETRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${s_medicine}, 'AZM.TAB') </t>
+  </si>
+  <si>
+    <t>Was the population informed before the campaign?</t>
+  </si>
+  <si>
+    <t>Social Mobilisation</t>
+  </si>
+  <si>
+    <t>Communication channels used</t>
+  </si>
+  <si>
+    <t>Area of supervision</t>
+  </si>
+  <si>
+    <t>Number of distributors supervised</t>
+  </si>
+  <si>
+    <t>Number of villages supervised</t>
+  </si>
+  <si>
+    <t>Challenges encountered</t>
+  </si>
+  <si>
+    <t>Proposed solutions</t>
+  </si>
+  <si>
+    <t>Supervisor recommendations</t>
+  </si>
+  <si>
+    <t>Were any adverse effects reported?</t>
+  </si>
+  <si>
+    <t>Were any serious adverse effects reported?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${s_medicine}, 'AZM.SUSP') </t>
+  </si>
+  <si>
+    <t>channel_com</t>
+  </si>
+  <si>
+    <t>select_multiple channel_com</t>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>Regional</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>select_one supervisor</t>
+  </si>
+  <si>
+    <t>s_supervisor_Level</t>
+  </si>
+  <si>
+    <t>Supervisor level</t>
+  </si>
+  <si>
+    <t>Health_facility</t>
+  </si>
+  <si>
+    <t>(Demo) 5. MDA Supervision Health facility V3</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_5_supervision_hf_v3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1078,6 +1117,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1131,7 +1184,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1194,6 +1247,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,6 +1272,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Tinkitina Benjamin" id="{469CF176-177D-4BA0-8B7A-054AB4CDC2FF}" userId="c23755edcbb30cff" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1495,9 +1563,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H43" dT="2026-04-01T12:33:20.38" personId="{469CF176-177D-4BA0-8B7A-054AB4CDC2FF}" id="{018D13DF-1012-4DF6-A96B-1024C4E8D7EC}">
+    <text>Change to AZM.SUP</text>
+  </threadedComment>
+  <threadedComment ref="H48" dT="2026-04-01T12:33:00.87" personId="{469CF176-177D-4BA0-8B7A-054AB4CDC2FF}" id="{45C6829E-2510-407D-9D1B-3CE01D387F3B}">
+    <text>Change to AZM.TAB</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
@@ -1516,7 +1595,7 @@
     <col min="14" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1524,60 +1603,60 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="10"/>
@@ -1594,15 +1673,15 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5"/>
@@ -1621,15 +1700,15 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
@@ -1642,7 +1721,7 @@
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="16" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1650,15 +1729,15 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
@@ -1671,7 +1750,7 @@
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="16" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1679,15 +1758,15 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
@@ -1700,7 +1779,7 @@
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="22" t="s">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1708,42 +1787,42 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
+    <row r="7" spans="1:17" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K7" s="29"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
@@ -1762,55 +1841,47 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:21" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="10" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-    </row>
-    <row r="10" spans="1:21" s="17" customFormat="1" ht="374.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>208</v>
-      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="20"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
       <c r="J10" s="10" t="s">
@@ -1823,57 +1894,59 @@
       <c r="O10" s="16"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-    </row>
-    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    </row>
+    <row r="11" spans="1:17" s="17" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5" t="s">
+      <c r="B12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
@@ -1882,15 +1955,15 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5"/>
@@ -1909,15 +1982,15 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5"/>
@@ -1926,7 +1999,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -1936,23 +2009,21 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="5" t="s">
-        <v>186</v>
-      </c>
+      <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
         <v>13</v>
@@ -1965,19 +2036,27 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
+        <v>287</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>168</v>
+      </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -1987,70 +2066,64 @@
       <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="B18" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>309</v>
+        <v>187</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>310</v>
+        <v>219</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
@@ -2071,13 +2144,13 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>311</v>
+        <v>203</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>314</v>
+        <v>220</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5"/>
@@ -2098,13 +2171,13 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>312</v>
+        <v>188</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>315</v>
+        <v>221</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5"/>
@@ -2125,23 +2198,17 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>316</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="6"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -2151,41 +2218,43 @@
       <c r="Q22" s="5"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
+      <c r="A23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>322</v>
+        <v>189</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>319</v>
+        <v>224</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
@@ -2206,13 +2275,13 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>323</v>
+        <v>204</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
@@ -2233,13 +2302,13 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>321</v>
+        <v>226</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
@@ -2260,23 +2329,17 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>325</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="6"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -2286,64 +2349,70 @@
       <c r="Q27" s="5"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
+      <c r="A28" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
+      <c r="A29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5"/>
@@ -2364,13 +2433,13 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
@@ -2391,23 +2460,17 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>254</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="6"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
@@ -2417,64 +2480,70 @@
       <c r="Q32" s="5"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
+      <c r="A33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
+      <c r="A34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5"/>
@@ -2495,13 +2564,13 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
@@ -2522,23 +2591,17 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>259</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="6"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
@@ -2548,64 +2611,70 @@
       <c r="Q37" s="5"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
+      <c r="A38" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="24"/>
+      <c r="A39" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="5"/>
@@ -2626,13 +2695,13 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5"/>
@@ -2653,23 +2722,17 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>263</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="6"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
-      <c r="J42" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
@@ -2679,64 +2742,70 @@
       <c r="Q42" s="5"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
+      <c r="A43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="24"/>
+      <c r="N43" s="24"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="24"/>
+      <c r="Q43" s="24"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="24"/>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="24"/>
+      <c r="A44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5"/>
@@ -2757,13 +2826,13 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5"/>
@@ -2784,23 +2853,17 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>267</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="6"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-      <c r="J47" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
@@ -2810,64 +2873,70 @@
       <c r="Q47" s="5"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
+      <c r="A48" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="24"/>
+      <c r="Q48" s="24"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="24"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="24"/>
+      <c r="A49" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5"/>
@@ -2888,13 +2957,13 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5"/>
@@ -2915,23 +2984,17 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>271</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="6"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
-      <c r="J52" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
@@ -2941,64 +3004,70 @@
       <c r="Q52" s="5"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
+      <c r="A53" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="I53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="24"/>
+      <c r="N53" s="24"/>
+      <c r="O53" s="24"/>
+      <c r="P53" s="24"/>
+      <c r="Q53" s="24"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="24"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="24"/>
-      <c r="N54" s="24"/>
-      <c r="O54" s="24"/>
-      <c r="P54" s="24"/>
-      <c r="Q54" s="24"/>
+      <c r="A54" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="6"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5"/>
@@ -3019,13 +3088,13 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5"/>
@@ -3046,23 +3115,17 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>275</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="6"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
-      <c r="J57" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
@@ -3072,9 +3135,7 @@
       <c r="Q57" s="5"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -3093,43 +3154,41 @@
       <c r="Q58" s="5"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="24" t="s">
+      <c r="A59" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24" t="s">
+      <c r="B59" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59" s="6"/>
+      <c r="E59" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="I59" s="24"/>
-      <c r="J59" s="24"/>
-      <c r="K59" s="24"/>
-      <c r="L59" s="24"/>
-      <c r="M59" s="24"/>
-      <c r="N59" s="24"/>
-      <c r="O59" s="24"/>
-      <c r="P59" s="24"/>
-      <c r="Q59" s="24"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>229</v>
+        <v>92</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>277</v>
+        <v>63</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="5"/>
@@ -3150,13 +3209,13 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>239</v>
+        <v>93</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>278</v>
+        <v>64</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="5"/>
@@ -3177,13 +3236,13 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>230</v>
+        <v>94</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>279</v>
+        <v>65</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="5"/>
@@ -3204,7 +3263,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="6"/>
@@ -3224,43 +3283,41 @@
       <c r="Q63" s="5"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="24" t="s">
+      <c r="A64" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B64" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24" t="s">
+      <c r="B64" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I64" s="24"/>
-      <c r="J64" s="24"/>
-      <c r="K64" s="24"/>
-      <c r="L64" s="24"/>
-      <c r="M64" s="24"/>
-      <c r="N64" s="24"/>
-      <c r="O64" s="24"/>
-      <c r="P64" s="24"/>
-      <c r="Q64" s="24"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>231</v>
+        <v>96</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>76</v>
+        <v>297</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="5"/>
@@ -3281,13 +3338,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>52</v>
+        <v>310</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>240</v>
+        <v>97</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="5"/>
@@ -3308,23 +3365,17 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="6"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
-      <c r="J67" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
@@ -3335,12 +3386,18 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>300</v>
+      </c>
       <c r="D68" s="6"/>
-      <c r="E68" s="5"/>
+      <c r="E68" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
       <c r="H68" s="5"/>
@@ -3355,16 +3412,24 @@
       <c r="Q68" s="5"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="6"/>
+      <c r="A69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>301</v>
+      </c>
       <c r="D69" s="6"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
+      <c r="J69" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
@@ -3375,23 +3440,23 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="D70" s="6"/>
-      <c r="E70" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="J70" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
@@ -3402,23 +3467,17 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
-      <c r="J71" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
@@ -3429,23 +3488,23 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="D72" s="6"/>
-      <c r="E72" s="5"/>
+      <c r="E72" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="J72" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
@@ -3456,13 +3515,13 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="5"/>
@@ -3483,17 +3542,23 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>307</v>
+      </c>
       <c r="D74" s="6"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
+      <c r="J74" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
@@ -3504,18 +3569,12 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="6"/>
       <c r="D75" s="6"/>
-      <c r="E75" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
       <c r="H75" s="5"/>
@@ -3531,13 +3590,13 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>17</v>
+        <v>303</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="5"/>
@@ -3546,7 +3605,7 @@
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
@@ -3558,13 +3617,13 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>19</v>
+        <v>304</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="5"/>
@@ -3573,7 +3632,7 @@
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
@@ -3585,17 +3644,23 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>305</v>
+      </c>
       <c r="D78" s="6"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="6"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
+      <c r="J78" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
@@ -3605,19 +3670,11 @@
       <c r="Q78" s="5"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="6"/>
       <c r="D79" s="6"/>
-      <c r="E79" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="6"/>
       <c r="H79" s="5"/>
@@ -3633,23 +3690,19 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="6"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
-      <c r="J80" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="J80" s="5"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
@@ -3660,23 +3713,19 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" s="6"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
-      <c r="J81" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
@@ -3685,497 +3734,246 @@
       <c r="P81" s="5"/>
       <c r="Q81" s="5"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="5"/>
-      <c r="L82" s="5"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
-      <c r="O82" s="5"/>
-      <c r="P82" s="5"/>
-      <c r="Q82" s="5"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D83" s="6"/>
-      <c r="E83" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="5"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="5"/>
-      <c r="L83" s="5"/>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
-      <c r="O83" s="5"/>
-      <c r="P83" s="5"/>
-      <c r="Q83" s="5"/>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K84" s="5"/>
-      <c r="L84" s="5"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" s="6"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="5"/>
-      <c r="J85" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K85" s="5"/>
-      <c r="L85" s="5"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
-      <c r="O85" s="5"/>
-      <c r="P85" s="5"/>
-      <c r="Q85" s="5"/>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="5"/>
-      <c r="K86" s="5"/>
-      <c r="L86" s="5"/>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5"/>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="5"/>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87" s="6"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K87" s="5"/>
-      <c r="L87" s="5"/>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
-      <c r="O87" s="5"/>
-      <c r="P87" s="5"/>
-      <c r="Q87" s="5"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D88" s="6"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K88" s="5"/>
-      <c r="L88" s="5"/>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
-      <c r="O88" s="5"/>
-      <c r="P88" s="5"/>
-      <c r="Q88" s="5"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D89" s="6"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K89" s="5"/>
-      <c r="L89" s="5"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="5"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="5"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="5"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="5"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:Q57" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>125</v>
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="E1" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="27" t="s">
-        <v>156</v>
-      </c>
       <c r="G1" s="27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="16"/>
+        <v>69</v>
+      </c>
+      <c r="D2" s="18"/>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
-    </row>
-    <row r="3" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="D3" s="18"/>
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="16"/>
+        <v>71</v>
+      </c>
+      <c r="D4" s="18"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="16"/>
+        <v>72</v>
+      </c>
+      <c r="D5" s="18"/>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-    </row>
-    <row r="6" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="16"/>
+        <v>73</v>
+      </c>
+      <c r="D6" s="18"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
-    </row>
-    <row r="7" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="16"/>
+        <v>74</v>
+      </c>
+      <c r="D7" s="18"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="D8" s="18"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="D9" s="18"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
-    </row>
-    <row r="10" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="D10" s="18"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="16"/>
+        <v>78</v>
+      </c>
+      <c r="D11" s="18"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="16"/>
+        <v>79</v>
+      </c>
+      <c r="D12" s="18"/>
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
-    </row>
-    <row r="13" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="D13" s="18"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
-    </row>
-    <row r="14" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B14" s="14">
         <v>99</v>
@@ -4183,1660 +3981,1907 @@
       <c r="C14" s="19">
         <v>99</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
-    </row>
-    <row r="15" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="14"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="16"/>
+      <c r="D15" s="19"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="D16" s="6"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="D17" s="6"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="5"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="D19" s="6"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="D20" s="6"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="D21" s="6"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="D22" s="6"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="D23" s="6"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" s="6"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>32</v>
+        <v>311</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>184</v>
+        <v>312</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="5"/>
+        <v>312</v>
+      </c>
+      <c r="D26" s="6"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>32</v>
+        <v>311</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>185</v>
+        <v>313</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="5"/>
+        <v>313</v>
+      </c>
+      <c r="D27" s="6"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>32</v>
+        <v>311</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>50</v>
+        <v>314</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="5"/>
+        <v>314</v>
+      </c>
+      <c r="D28" s="6"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>32</v>
+        <v>311</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="D29" s="6"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="6"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-    </row>
-    <row r="32" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-    </row>
-    <row r="33" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-    </row>
-    <row r="34" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-    </row>
-    <row r="35" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-    </row>
-    <row r="36" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-    </row>
-    <row r="37" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-    </row>
-    <row r="38" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D38" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="D38" s="20"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
-    </row>
-    <row r="39" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="D39" s="16"/>
+        <v>171</v>
+      </c>
+      <c r="D39" s="20"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
-    </row>
-    <row r="40" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H39" s="16"/>
+    </row>
+    <row r="40" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D40" s="16"/>
+        <v>172</v>
+      </c>
+      <c r="D40" s="20"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
       <c r="G40" s="16"/>
-    </row>
-    <row r="41" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H40" s="16"/>
+    </row>
+    <row r="41" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" s="16"/>
+        <v>173</v>
+      </c>
+      <c r="D41" s="20"/>
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
-    </row>
-    <row r="42" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="D42" s="16"/>
+        <v>174</v>
+      </c>
+      <c r="D42" s="20"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
-    </row>
-    <row r="43" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="D43" s="16"/>
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
       <c r="G43" s="16"/>
-    </row>
-    <row r="44" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H43" s="16"/>
+    </row>
+    <row r="44" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="D44" s="16"/>
+        <v>176</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>171</v>
+      </c>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
       <c r="G44" s="16"/>
-    </row>
-    <row r="45" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="D45" s="16"/>
+        <v>177</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>170</v>
+      </c>
       <c r="E45" s="16"/>
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
-    </row>
-    <row r="46" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="D46" s="16"/>
+        <v>178</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>170</v>
+      </c>
       <c r="E46" s="16"/>
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
-    </row>
-    <row r="47" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="16"/>
+      <c r="H46" s="16"/>
+    </row>
+    <row r="47" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>173</v>
+      </c>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H47" s="16"/>
+    </row>
+    <row r="48" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+    </row>
+    <row r="50" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+    </row>
+    <row r="51" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+    </row>
+    <row r="52" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+    </row>
+    <row r="53" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+    </row>
+    <row r="54" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+    </row>
+    <row r="55" spans="1:8" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D56" s="5"/>
+        <v>108</v>
+      </c>
+      <c r="D56" s="6"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="5"/>
+        <v>109</v>
+      </c>
+      <c r="D57" s="6"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="16"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="5"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58" s="6"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H58" s="5"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>126</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D59" s="6"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>126</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D60" s="6"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>127</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D61" s="6"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>127</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="D62" s="6"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>128</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D63" s="6"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>128</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="D64" s="6"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>129</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D65" s="6"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>129</v>
-      </c>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="16"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E67" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E68" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E70" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="D70" s="6"/>
+      <c r="E70" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E71" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="D71" s="6"/>
+      <c r="E71" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E72" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E73" s="5"/>
+        <v>124</v>
+      </c>
+      <c r="D73" s="6"/>
+      <c r="E73" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E74" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="D74" s="6"/>
+      <c r="E74" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E75" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="D75" s="6"/>
+      <c r="E75" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E76" s="5"/>
+        <v>127</v>
+      </c>
+      <c r="D76" s="6"/>
+      <c r="E76" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E77" s="5"/>
+        <v>128</v>
+      </c>
+      <c r="D77" s="6"/>
+      <c r="E77" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D79" s="6"/>
+      <c r="E79" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>156</v>
+      <c r="H79" s="5"/>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D80" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="D80" s="6"/>
       <c r="E80" s="5" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>156</v>
+      <c r="H80" s="5"/>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D81" s="5"/>
+        <v>132</v>
+      </c>
+      <c r="D81" s="6"/>
       <c r="E81" s="5" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>156</v>
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D82" s="5"/>
+        <v>133</v>
+      </c>
+      <c r="D82" s="6"/>
       <c r="E82" s="5" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>156</v>
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D83" s="5"/>
+        <v>134</v>
+      </c>
+      <c r="D83" s="6"/>
       <c r="E83" s="5" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
-        <v>156</v>
+      <c r="H83" s="5"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D84" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="D84" s="6"/>
       <c r="E84" s="5" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>156</v>
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D85" s="5"/>
+        <v>136</v>
+      </c>
+      <c r="D85" s="6"/>
       <c r="E85" s="5" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>156</v>
+      <c r="H85" s="5"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D86" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="D86" s="6"/>
       <c r="E86" s="5" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5" t="s">
-        <v>154</v>
-      </c>
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="5"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D88" s="6"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="C89" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D89" s="6"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D92" s="6"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D93" s="6"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5" t="s">
+      <c r="C94" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D94" s="6"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D95" s="6"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5" t="s">
+      <c r="C97" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D97" s="6"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D98" s="6"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C100" s="25"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C100" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D100" s="6"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>284</v>
+        <v>152</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D101" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="D101" s="6"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G101" s="5"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>285</v>
+        <v>153</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D102" s="5"/>
+        <v>153</v>
+      </c>
+      <c r="D102" s="6"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="G102" s="5"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>286</v>
+        <v>154</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D103" s="5"/>
+        <v>154</v>
+      </c>
+      <c r="D103" s="6"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="G103" s="5"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>287</v>
+        <v>155</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D104" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="D104" s="6"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="G104" s="5"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H104" s="5"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D105" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="D105" s="6"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="G105" s="5"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" s="5"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>289</v>
+        <v>157</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D106" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="D106" s="6"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="G106" s="5"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="D107" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="D107" s="6"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C108" s="25"/>
+      <c r="D108" s="25"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D110" s="6"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D111" s="6"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D112" s="6"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D113" s="6"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D114" s="6"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D116" s="6"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H116" s="5"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D117" s="6"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G107" s="5"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G108" s="5"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G109" s="5"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G110" s="5"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G111" s="5"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G112" s="5"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G113" s="5"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G114" s="5"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="G115" s="5"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G116" s="5"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G117" s="5"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="D118" s="5"/>
+        <v>260</v>
+      </c>
+      <c r="D118" s="6"/>
       <c r="E118" s="5"/>
-      <c r="F118" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="G118" s="5"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F118" s="5"/>
+      <c r="G118" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H118" s="5"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D119" s="5"/>
+        <v>261</v>
+      </c>
+      <c r="D119" s="6"/>
       <c r="E119" s="5"/>
-      <c r="F119" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G119" s="5"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F119" s="5"/>
+      <c r="G119" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H119" s="5"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="D120" s="5"/>
+        <v>262</v>
+      </c>
+      <c r="D120" s="6"/>
       <c r="E120" s="5"/>
-      <c r="F120" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G120" s="5"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H120" s="5"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D121" s="6"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H121" s="5"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D122" s="6"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H122" s="5"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D123" s="6"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H123" s="5"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D124" s="6"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H124" s="5"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D125" s="6"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H125" s="5"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D126" s="6"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H126" s="5"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H127" s="5"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D128" s="6"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H128" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5856,25 +5901,25 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Demo/MDA/demo_mda_9999_5_supervision_hf.xlsx
+++ b/Demo/MDA/demo_mda_9999_5_supervision_hf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25BC8D4-7FB7-4952-B9A5-102E23ED30F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0859B9-B591-48FC-99CB-C6B95F5D358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -880,9 +880,6 @@
   </si>
   <si>
     <t>disease_filter</t>
-  </si>
-  <si>
-    <t>selected(${s_disease}, disease_filter)</t>
   </si>
   <si>
     <t>not(
@@ -1063,6 +1060,9 @@
   </si>
   <si>
     <t>demo_mda_9999_5_supervision_hf_v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> selected(${s_disease}, disease_filter)</t>
   </si>
 </sst>
 </file>
@@ -1789,13 +1789,13 @@
     </row>
     <row r="7" spans="1:17" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="30" t="s">
         <v>317</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>318</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="29"/>
@@ -1908,7 +1908,7 @@
       <c r="D11" s="20"/>
       <c r="E11" s="16"/>
       <c r="F11" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G11" s="23" t="s">
         <v>186</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="28" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>57</v>
@@ -2091,7 +2091,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>222</v>
@@ -2222,7 +2222,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>223</v>
@@ -2353,7 +2353,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>227</v>
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>231</v>
@@ -2615,7 +2615,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>235</v>
@@ -2746,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C43" s="24" t="s">
         <v>239</v>
@@ -2758,7 +2758,7 @@
       <c r="F43" s="24"/>
       <c r="G43" s="24"/>
       <c r="H43" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I43" s="24"/>
       <c r="J43" s="24"/>
@@ -2877,7 +2877,7 @@
         <v>10</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C48" s="24" t="s">
         <v>243</v>
@@ -2889,7 +2889,7 @@
       <c r="F48" s="24"/>
       <c r="G48" s="24"/>
       <c r="H48" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I48" s="24"/>
       <c r="J48" s="24"/>
@@ -3008,7 +3008,7 @@
         <v>10</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C53" s="24" t="s">
         <v>58</v>
@@ -3290,7 +3290,7 @@
         <v>95</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="5" t="s">
@@ -3317,7 +3317,7 @@
         <v>96</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="5"/>
@@ -3338,13 +3338,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="5"/>
@@ -3392,7 +3392,7 @@
         <v>98</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="5" t="s">
@@ -3419,7 +3419,7 @@
         <v>99</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="5"/>
@@ -3446,7 +3446,7 @@
         <v>100</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="5"/>
@@ -3521,7 +3521,7 @@
         <v>103</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="5"/>
@@ -3548,7 +3548,7 @@
         <v>104</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="5"/>
@@ -3596,7 +3596,7 @@
         <v>102</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="5"/>
@@ -3623,7 +3623,7 @@
         <v>105</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="5"/>
@@ -3650,7 +3650,7 @@
         <v>106</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="5"/>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>162</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>163</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>164</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>29</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>165</v>
@@ -4121,13 +4121,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
@@ -4147,13 +4147,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>312</v>
-      </c>
       <c r="C26" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
@@ -4163,13 +4163,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
@@ -4179,13 +4179,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5"/>
@@ -4195,13 +4195,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
@@ -4211,10 +4211,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>50</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>18</v>
@@ -4253,7 +4253,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>166</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>167</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>33</v>
@@ -4301,7 +4301,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>34</v>
@@ -4492,10 +4492,10 @@
         <v>175</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>174</v>
@@ -4506,10 +4506,10 @@
         <v>175</v>
       </c>
       <c r="B49" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>291</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>292</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>174</v>
@@ -4524,10 +4524,10 @@
         <v>175</v>
       </c>
       <c r="B50" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C50" s="20" t="s">
         <v>293</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>294</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>174</v>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" t="s">
         <v>320</v>
-      </c>
-      <c r="B2" t="s">
-        <v>321</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
